--- a/Result/profitability/3131.xlsx
+++ b/Result/profitability/3131.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.97</v>
       </c>
       <c r="M2" t="n">
-        <v>10.07375</v>
+        <v>10.54375</v>
       </c>
       <c r="N2" t="n">
-        <v>41.52375</v>
+        <v>40.3675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>9.17625</v>
+        <v>9.493749999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>40.665</v>
+        <v>39.76875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>8.05875</v>
+        <v>8.36375</v>
       </c>
       <c r="N4" t="n">
-        <v>40.785</v>
+        <v>40.54125000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>2.63</v>
       </c>
       <c r="M5" t="n">
-        <v>7.295</v>
+        <v>7.81125</v>
       </c>
       <c r="N5" t="n">
-        <v>39.73125</v>
+        <v>39.51625000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>6.35625</v>
+        <v>6.45375</v>
       </c>
       <c r="N6" t="n">
-        <v>36.08375</v>
+        <v>35.84875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.66</v>
       </c>
       <c r="M7" t="n">
-        <v>5.138750000000001</v>
+        <v>4.12875</v>
       </c>
       <c r="N7" t="n">
-        <v>34.86750000000001</v>
+        <v>34.4625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.99</v>
       </c>
       <c r="M8" t="n">
-        <v>2.855</v>
+        <v>2.23875</v>
       </c>
       <c r="N8" t="n">
-        <v>34.50125</v>
+        <v>35.13625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9572,6 +9572,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1727</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1056</v>
+      </c>
+      <c r="E73" t="n">
+        <v>671</v>
+      </c>
+      <c r="F73" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="G73" t="n">
+        <v>365</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>21.14%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>41</v>
+      </c>
+      <c r="J73" t="n">
+        <v>406</v>
+      </c>
+      <c r="K73" t="n">
+        <v>324</v>
+      </c>
+      <c r="L73" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N73" t="n">
+        <v>41.37625</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-0.3060211049037864</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>5.079999999999998</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.1503848431024275</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.5858156028368795</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>-1.719999999999999</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>-0.04238541153277475</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
